--- a/grupos/corazonlatino/excel-campeonatos.xlsx
+++ b/grupos/corazonlatino/excel-campeonatos.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\deportazo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\deportazo\grupos\corazonlatino\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6429F56D-3F4B-4DDA-BD23-CC7EED23A96C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2666CB38-75C8-4D8D-B941-0CDCFADE22AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6AAC4C82-243A-49E8-898B-368379F134C3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="78">
   <si>
     <t>EQUIPO1</t>
   </si>
@@ -54,18 +54,12 @@
     <t>COLOR</t>
   </si>
   <si>
-    <t>ROSMERY</t>
-  </si>
-  <si>
     <t>YAMILETH</t>
   </si>
   <si>
     <t>JOEL</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
     <t>MARIA</t>
   </si>
   <si>
@@ -75,18 +69,9 @@
     <t>CARLES</t>
   </si>
   <si>
-    <t>JUAN</t>
-  </si>
-  <si>
-    <t>JEIK</t>
-  </si>
-  <si>
     <t>JAIME</t>
   </si>
   <si>
-    <t>ALEJANDRO</t>
-  </si>
-  <si>
     <t>ANDERSON</t>
   </si>
   <si>
@@ -99,33 +84,15 @@
     <t>EMILIO</t>
   </si>
   <si>
-    <t>DUDU</t>
-  </si>
-  <si>
-    <t>NUEVOS</t>
-  </si>
-  <si>
     <t>ABIGAIL</t>
   </si>
   <si>
     <t>EUNISE</t>
   </si>
   <si>
-    <t>JESSICA</t>
-  </si>
-  <si>
-    <t>LESLY</t>
-  </si>
-  <si>
     <t>NENDO</t>
   </si>
   <si>
-    <t>NICOLE</t>
-  </si>
-  <si>
-    <t>SARA</t>
-  </si>
-  <si>
     <t>YEAN POOL</t>
   </si>
   <si>
@@ -144,18 +111,12 @@
     <t>JOSUE MOLE</t>
   </si>
   <si>
-    <t>MARILUZ</t>
-  </si>
-  <si>
     <t>MAYER</t>
   </si>
   <si>
     <t>SADITH</t>
   </si>
   <si>
-    <t>SULI</t>
-  </si>
-  <si>
     <t>YORDI</t>
   </si>
   <si>
@@ -174,9 +135,6 @@
     <t>#</t>
   </si>
   <si>
-    <t>JOOSE</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -201,24 +159,15 @@
     <t>LUIS</t>
   </si>
   <si>
-    <t>CORAZON LATINO</t>
-  </si>
-  <si>
     <t>SORTEO CORAZÓN LATINO -FIN DE AÑO- EQUIPOS</t>
   </si>
   <si>
-    <t>SORTEO CORAZÓN LATINO -FIN DE AÑO - EQUIPOS</t>
-  </si>
-  <si>
     <t>MIEMBROS</t>
   </si>
   <si>
     <t>RONALD</t>
   </si>
   <si>
-    <t>FRANCO2</t>
-  </si>
-  <si>
     <t>HUGO</t>
   </si>
   <si>
@@ -228,21 +177,9 @@
     <t>CONFIRMADOS</t>
   </si>
   <si>
-    <t>INVITADOS</t>
-  </si>
-  <si>
-    <t>MARCELO</t>
-  </si>
-  <si>
     <t>GRIS</t>
   </si>
   <si>
-    <t>ROJO</t>
-  </si>
-  <si>
-    <t>ANDER</t>
-  </si>
-  <si>
     <t>VERDE</t>
   </si>
   <si>
@@ -253,6 +190,87 @@
   </si>
   <si>
     <t>AZUL</t>
+  </si>
+  <si>
+    <t>YAHYA</t>
+  </si>
+  <si>
+    <t>ELENA</t>
+  </si>
+  <si>
+    <t>SEBASTIAN</t>
+  </si>
+  <si>
+    <t>JOSE</t>
+  </si>
+  <si>
+    <t>LEZLIE</t>
+  </si>
+  <si>
+    <t>CORAZÓN LATINO</t>
+  </si>
+  <si>
+    <t>KEYLI</t>
+  </si>
+  <si>
+    <t>MELINA</t>
+  </si>
+  <si>
+    <t>HUMBERTO</t>
+  </si>
+  <si>
+    <t>RUTH</t>
+  </si>
+  <si>
+    <t>MAMA MILU</t>
+  </si>
+  <si>
+    <t>CRISTOPHER</t>
+  </si>
+  <si>
+    <t>EDWIN</t>
+  </si>
+  <si>
+    <t>SORTEO CORAZÓN LATINO - EQUIPOS</t>
+  </si>
+  <si>
+    <t>JOSUE</t>
+  </si>
+  <si>
+    <t>BRUNO</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>MILUSKA</t>
+  </si>
+  <si>
+    <t>HELENA</t>
+  </si>
+  <si>
+    <t>DEBYS</t>
+  </si>
+  <si>
+    <t>LUISITO</t>
+  </si>
+  <si>
+    <t>ROCIO</t>
+  </si>
+  <si>
+    <t>FELIPE</t>
+  </si>
+  <si>
+    <t>JASMIN</t>
+  </si>
+  <si>
+    <t>CRISTOFER 2</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>YORDY</t>
   </si>
 </sst>
 </file>
@@ -352,7 +370,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -482,19 +500,6 @@
       <left style="medium">
         <color theme="1"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -565,19 +570,6 @@
       <bottom style="thin">
         <color indexed="64"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color theme="1"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -715,11 +707,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -734,27 +739,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="2" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -765,101 +767,98 @@
     <xf numFmtId="1" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -942,82 +941,6 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>301381</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>251654</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>961035</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>109442</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8672B616-3CD7-4DE2-83FA-0CB5DF17A8C4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6035119" y="2487687"/>
-          <a:ext cx="2470965" cy="2506050"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst>
-            <a:gd name="adj" fmla="val 4167"/>
-          </a:avLst>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="76200" cap="sq">
-          <a:solidFill>
-            <a:srgbClr val="EAEAEA"/>
-          </a:solidFill>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:effectLst>
-          <a:reflection blurRad="12700" stA="33000" endPos="28000" dist="5000" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
-        </a:effectLst>
-        <a:scene3d>
-          <a:camera prst="orthographicFront"/>
-          <a:lightRig rig="threePt" dir="t">
-            <a:rot lat="0" lon="0" rev="2700000"/>
-          </a:lightRig>
-        </a:scene3d>
-        <a:sp3d contourW="6350">
-          <a:bevelT h="38100"/>
-          <a:contourClr>
-            <a:srgbClr val="C0C0C0"/>
-          </a:contourClr>
-        </a:sp3d>
       </xdr:spPr>
     </xdr:pic>
     <xdr:clientData/>
@@ -1436,46 +1359,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="41"/>
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="42"/>
+      <c r="A1" s="35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="36"/>
+      <c r="C1" s="36"/>
+      <c r="D1" s="36"/>
+      <c r="E1" s="36"/>
+      <c r="F1" s="37"/>
       <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="37"/>
-      <c r="E2" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="37"/>
+      <c r="A2" s="52" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="53"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="54"/>
     </row>
     <row r="3" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="3">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C3" s="3">
         <v>18</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="E3" s="8">
         <v>35</v>
       </c>
-      <c r="F3" s="6" t="s">
-        <v>22</v>
+      <c r="F3" s="31" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1484,21 +1405,21 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
         <f>C3+1</f>
         <v>19</v>
       </c>
-      <c r="D4" s="4" t="s">
-        <v>5</v>
+      <c r="D4" s="6" t="s">
+        <v>16</v>
       </c>
       <c r="E4" s="8">
         <f>E3+1</f>
         <v>36</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1507,21 +1428,21 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>13</v>
+        <v>51</v>
       </c>
       <c r="C5" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" s="8">
+        <f t="shared" ref="E5:E11" si="1">E4+1</f>
         <v>37</v>
       </c>
-      <c r="E5" s="8">
-        <f t="shared" ref="E5:E14" si="1">E4+1</f>
-        <v>37</v>
-      </c>
       <c r="F5" s="6" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1530,74 +1451,74 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>38</v>
+      <c r="D6" s="6" t="s">
+        <v>18</v>
       </c>
       <c r="E6" s="8">
         <f t="shared" si="1"/>
         <v>38</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J6" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
+        <v>57</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
     </row>
     <row r="7" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>15</v>
+      <c r="B7" s="6" t="s">
+        <v>39</v>
       </c>
       <c r="C7" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="E7" s="8">
         <f t="shared" si="1"/>
         <v>39</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J7" s="30" t="s">
-        <v>44</v>
-      </c>
-      <c r="K7" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="J7" s="27" t="s">
+        <v>31</v>
+      </c>
+      <c r="K7" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="29" t="s">
+      <c r="N7" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="O7" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="P7" s="29" t="s">
-        <v>49</v>
+      <c r="O7" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="P7" s="26" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -1606,43 +1527,41 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E8" s="8">
         <f t="shared" si="1"/>
         <v>40</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="23">
+        <v>59</v>
+      </c>
+      <c r="J8" s="22">
         <v>1</v>
       </c>
-      <c r="K8" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="N8" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>19</v>
-      </c>
+      <c r="K8" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="L8" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="M8" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="N8" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="O8" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="P8" s="7"/>
     </row>
     <row r="9" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A9" s="2">
@@ -1650,43 +1569,41 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="C9" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E9" s="8">
         <f t="shared" si="1"/>
         <v>41</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J9" s="24">
+        <v>60</v>
+      </c>
+      <c r="J9" s="23">
         <v>2</v>
       </c>
-      <c r="K9" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="N9" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>36</v>
-      </c>
+      <c r="K9" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="M9" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="N9" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="O9" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="P9" s="7"/>
     </row>
     <row r="10" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A10" s="2">
@@ -1694,43 +1611,41 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="8">
         <f t="shared" si="1"/>
         <v>42</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="24">
+        <v>61</v>
+      </c>
+      <c r="J10" s="23">
         <v>3</v>
       </c>
-      <c r="K10" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="M10" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="N10" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>25</v>
-      </c>
+      <c r="K10" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="M10" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="N10" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="O10" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="P10" s="7"/>
     </row>
     <row r="11" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A11" s="2">
@@ -1738,87 +1653,78 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C11" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="D11" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="8">
         <f t="shared" si="1"/>
         <v>43</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="J11" s="24">
+        <v>62</v>
+      </c>
+      <c r="J11" s="23">
         <v>4</v>
       </c>
-      <c r="K11" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="N11" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>53</v>
-      </c>
+      <c r="K11" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="M11" s="32" t="s">
+        <v>21</v>
+      </c>
+      <c r="N11" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="O11" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="P11" s="7"/>
     </row>
     <row r="12" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>20</v>
+      <c r="B12" s="6" t="s">
+        <v>15</v>
       </c>
       <c r="C12" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="17">
-        <f t="shared" si="1"/>
-        <v>44</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="24">
+        <v>29</v>
+      </c>
+      <c r="E12" s="16"/>
+      <c r="F12" s="6"/>
+      <c r="J12" s="23">
         <v>5</v>
       </c>
-      <c r="K12" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="N12" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>52</v>
-      </c>
+      <c r="K12" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="M12" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="N12" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="O12" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="P12" s="7"/>
     </row>
     <row r="13" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A13" s="2">
@@ -1826,43 +1732,36 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C13" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E13" s="19">
-        <f t="shared" si="1"/>
-        <v>45</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="24">
+        <v>38</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="6"/>
+      <c r="J13" s="23">
         <v>6</v>
       </c>
-      <c r="K13" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="M13" s="10" t="s">
-        <v>47</v>
-      </c>
-      <c r="N13" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>22</v>
-      </c>
+      <c r="K13" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="L13" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="M13" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="N13" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="O13" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="P13" s="7"/>
     </row>
     <row r="14" spans="1:16" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A14" s="2">
@@ -1870,42 +1769,37 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C14" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E14" s="19">
-        <f t="shared" si="1"/>
+        <v>30</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="6"/>
+      <c r="J14" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="K14" s="25" t="s">
         <v>46</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>4</v>
-      </c>
-      <c r="K14" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="L14" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="M14" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="O14" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="P14" s="32" t="s">
-        <v>71</v>
+      <c r="L14" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="M14" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="N14" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="O14" s="30" t="s">
+        <v>49</v>
+      </c>
+      <c r="P14" s="29" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
@@ -1914,19 +1808,17 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C15" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="37"/>
+        <v>13</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:16" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="2">
@@ -1934,21 +1826,17 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="8">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>64</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="2">
@@ -1956,20 +1844,17 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C17" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="8">
-        <f t="shared" ref="E17:E19" si="2">E16+1</f>
-        <v>2</v>
-      </c>
-      <c r="F17" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="2">
@@ -1977,20 +1862,17 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" s="20">
+        <v>53</v>
+      </c>
+      <c r="C18" s="19">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="D18" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="8">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="F18" s="4"/>
+      <c r="D18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="6"/>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="2">
@@ -1998,140 +1880,135 @@
         <v>17</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="C19" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="8">
-        <f t="shared" si="2"/>
-        <v>4</v>
-      </c>
-      <c r="F19" s="4"/>
+      <c r="D19" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="15"/>
-      <c r="F20" s="18"/>
+      <c r="F20" s="17"/>
     </row>
     <row r="21" spans="1:6" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="53" t="s">
-        <v>46</v>
-      </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="49"/>
-      <c r="D21" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="E21" s="49"/>
-      <c r="F21" s="50"/>
+      <c r="A21" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="B21" s="44"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="44"/>
+      <c r="F21" s="45"/>
     </row>
     <row r="22" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54">
+      <c r="A22" s="49">
         <f>MAX(A3:A19,C3:C19,E3:E19)</f>
-        <v>46</v>
-      </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="51">
+        <v>43</v>
+      </c>
+      <c r="B22" s="50"/>
+      <c r="C22" s="50"/>
+      <c r="D22" s="46">
         <f>COUNTA(K8:P13)</f>
-        <v>36</v>
-      </c>
-      <c r="E22" s="51"/>
-      <c r="F22" s="52"/>
+        <v>30</v>
+      </c>
+      <c r="E22" s="46"/>
+      <c r="F22" s="47"/>
     </row>
     <row r="23" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="56"/>
-      <c r="B23" s="55"/>
-      <c r="C23" s="55"/>
-      <c r="D23" s="51"/>
-      <c r="E23" s="51"/>
-      <c r="F23" s="52"/>
+      <c r="A23" s="51"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="50"/>
+      <c r="D23" s="46"/>
+      <c r="E23" s="46"/>
+      <c r="F23" s="47"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="43"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
-      <c r="D24" s="44"/>
-      <c r="E24" s="44"/>
-      <c r="F24" s="45"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="39"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="40"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="43"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
-      <c r="D25" s="44"/>
-      <c r="E25" s="44"/>
-      <c r="F25" s="45"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="39"/>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="40"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="43"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
-      <c r="D26" s="44"/>
-      <c r="E26" s="44"/>
-      <c r="F26" s="45"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="39"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="40"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="43"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
-      <c r="D27" s="44"/>
-      <c r="E27" s="44"/>
-      <c r="F27" s="45"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="39"/>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="40"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="45"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="40"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="43"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="45"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="39"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="40"/>
     </row>
     <row r="30" spans="1:6" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="43"/>
-      <c r="B30" s="44"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="45"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="39"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="40"/>
     </row>
     <row r="31" spans="1:6" ht="65.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="46"/>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="48"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="42"/>
+      <c r="C31" s="42"/>
+      <c r="D31" s="42"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="43"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="8">
     <mergeCell ref="J6:P6"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A24:F31"/>
-    <mergeCell ref="E2:F2"/>
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D22:F23"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A22:C23"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="E2 F3:F14 B3:D19 E15 F16:F19 B20:F20 A21:A22 A24 C32">
+  <conditionalFormatting sqref="B3:D19 F3:F19 B20:F20 A21:A22 A24 C32">
     <cfRule type="expression" dxfId="1" priority="13">
-      <formula>COUNTIF($K$8:$P$14,A2)&gt;0</formula>
+      <formula>COUNTIF($K$8:$P$14,A3)&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2142,7 +2019,7 @@
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
           <x14:cfRule type="expression" priority="14" id="{00000000-000E-0000-0000-000004000000}">
-            <xm:f>COUNTIF(LISTA!$B$3:$I$9,A2)&gt;0</xm:f>
+            <xm:f>COUNTIF(LISTA!$B$3:$I$9,A3)&gt;0</xm:f>
             <x14:dxf>
               <fill>
                 <patternFill>
@@ -2151,7 +2028,7 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <xm:sqref>E2 F3:F14 B3:D19 E15 F16:F19 B20:F20 A21:A22 A24 C32</xm:sqref>
+          <xm:sqref>B3:D19 F3:F19 B20:F20 A21:A22 A24 C32</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2169,21 +2046,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="57" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="59"/>
+      <c r="A1" s="55" t="s">
+        <v>40</v>
+      </c>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" spans="1:9" ht="29.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A2" s="13" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>0</v>
@@ -2198,25 +2075,23 @@
         <v>2</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="30" thickTop="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
+      <c r="B3" s="7"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
